--- a/stories/arbres/TREE-EMO-010.xlsx
+++ b/stories/arbres/TREE-EMO-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le pommier, Jules a rempli un petit panier. C'était long. Il a porté, posé, recommencé. Le dos se redresse. Papa dit : quel effort. Maman arrive avec l'eau. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Sous le pommier, Jules a rempli un petit panier. C'était long. Il a porté, posé, recommencé. Le dos se redresse. Quel effort. Maman arrive avec l'eau. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sous le pommier, Jules a rempli un petit panier. C'était long. Il a porté, posé, recommencé. Le dos se redresse.
+papa|Quel effort. Maman arrive avec l'eau.
+narrateur|Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1512,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1541,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a aidé près du train-jouet. Il est fier de l'effort. C'est le train. La fenêtre tremble un tout petit peu. Jules s'approche, sans courir. Maman n'est pas loin. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a aidé près du train-jouet. Il est fier de l'effort. C'est le train. La fenêtre tremble un tout petit peu. Jules s'approche, sans courir. Maman n'est pas loin. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1679,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a aidé près du train-jouet. Il est fier de l'effort. C'est le train. La fenêtre tremble un tout petit peu. Jules s'approche, sans courir. Maman n'est pas loin. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1867,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a fini un effort. Quel mot dit-on ? Avec le train.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1855,7 +1896,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules retient le geste. Il respire.</t>
+          <t>Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules retient le geste. Il respire.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1997,6 +2038,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules retient le geste. Il respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2235,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2211,7 +2264,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Tom, après le train. La corbeille craque. Tom reste à sa place. Jules aussi. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Tom, après le train. La corbeille craque. Tom reste à sa place. Jules aussi. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2349,6 +2402,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Tom, après le train. La corbeille craque. Tom reste à sa place. Jules aussi. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2594,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2559,7 +2623,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après le train et Tom. La tasse est encore tiède. On dit merci. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. Le soleil est encore là.</t>
+          <t>Jules rejoint le matin, après le train et Tom. La tasse est encore tiède. On dit merci. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2697,6 +2761,13 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après le train et Tom. La tasse est encore tiède. On dit merci. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules quitte ce moment et va vers papa. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2930,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2883,7 +2959,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après le train et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. On gardu geste.</t>
+          <t>Jules rejoint après la sieste, après le train et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. On gardu geste.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3021,6 +3097,13 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après le train et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules nomme encore le mot, tout bas. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3266,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3207,7 +3295,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après le train et Tom. Une abeille bourdonne loin. On attend un petit moment. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules boit une gorgée. Il se sent plus léger. Papa et maman sont là.</t>
+          <t>Jules rejoint le soir, après le train et Tom. Une abeille bourdonne loin. On attend un petit moment. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules boit une gorgée. Il se sent plus léger. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3345,6 +3433,13 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après le train et Tom. Une abeille bourdonne loin. On attend un petit moment. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules boit une gorgée. Il se sent plus léger. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3602,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3631,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Léa, après le train. La fenêtre tremble un tout petit peu. Jules touche Léa tout doucement. Papa dit : je suis là. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Léa, après le train. La fenêtre tremble un tout petit peu. Jules touche Léa tout doucement. Je suis là. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3769,14 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Léa, après le train. La fenêtre tremble un tout petit peu. Jules touche Léa tout doucement.
+papa|Je suis là.
+narrateur|Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3963,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3992,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après le train et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules serre la main de papa, tout doux. On respire.</t>
+          <t>Jules rejoint le matin, après le train et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules serre la main de papa, tout doux. On respire.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4130,13 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après le train et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules serre la main de papa, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4299,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4203,7 +4328,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après le train et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. Merci, et au dodo bientôt.</t>
+          <t>Jules rejoint après la sieste, après le train et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4341,6 +4466,13 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après le train et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules quitte ce moment et va vers papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4635,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4664,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après le train et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
+          <t>Jules rejoint le soir, après le train et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4802,13 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après le train et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4971,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4851,7 +5000,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Sami, après le train. La pomme est croquante. Sami est là. Jules pose les mains à vue, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Sami, après le train. La pomme est croquante. Sami est là. Jules pose les mains à vue, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4989,6 +5138,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Sami, après le train. La pomme est croquante. Sami est là. Jules pose les mains à vue, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5330,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5199,7 +5359,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après le train et Sami. Un pigeon roucoule. On essuie une miette. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. On se serre un peu.</t>
+          <t>Jules rejoint le matin, après le train et Sami. Un pigeon roucoule. On essuie une miette. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. On se serre un peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5337,6 +5497,13 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après le train et Sami. Un pigeon roucoule. On essuie une miette. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules nomme encore le mot, tout bas. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5666,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5523,7 +5695,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après le train et Sami. La cuillère tinte. On referme un livre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules serre la main de papa, tout doux. On rentre.</t>
+          <t>Jules rejoint après la sieste, après le train et Sami. La cuillère tinte. On referme un livre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules serre la main de papa, tout doux. On rentre.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5661,6 +5833,13 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après le train et Sami. La cuillère tinte. On referme un livre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules serre la main de papa, tout doux. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +6002,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5847,7 +6031,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après le train et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules range le soir un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
+          <t>Jules rejoint le soir, après le train et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules range le soir un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5985,6 +6169,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après le train et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules range le soir un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6338,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6171,7 +6367,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules a porté un sac vers le bus. Il est fier de l'effort. Jules s'occupe du bus. La corbeille craque. Papa sourit. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a porté un sac vers le bus. Il est fier de l'effort. Jules s'occupe du bus. La corbeille craque. Papa sourit. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6309,6 +6505,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a porté un sac vers le bus. Il est fier de l'effort. Jules s'occupe du bus. La corbeille craque. Papa sourit. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6491,6 +6693,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a fini un effort. Quel mot dit-on ? Avec le bus.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6515,7 +6722,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules répète le mot. Papa hoche la tête.</t>
+          <t>Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6657,6 +6864,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules répète le mot. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7061,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6871,7 +7090,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Tom, après le bus. Un galet est lisse dans la main. Jules attend près de Tom. Il ne prend pas de force. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Tom, après le bus. Un galet est lisse dans la main. Jules attend près de Tom. Il ne prend pas de force. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7009,6 +7228,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Tom, après le bus. Un galet est lisse dans la main. Jules attend près de Tom. Il ne prend pas de force. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7420,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7449,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après le bus et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. On se dit à plus tard.</t>
+          <t>Jules rejoint le matin, après le bus et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7587,13 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après le bus et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules nomme encore le mot, tout bas. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7756,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7543,7 +7785,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après le bus et Tom. Le banc est tiède. On se tait une seconde. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. Le soleil est encore là.</t>
+          <t>Jules rejoint après la sieste, après le bus et Tom. Le banc est tiède. On se tait une seconde. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules nomme encore le mot, tout bas. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7681,6 +7923,13 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après le bus et Tom. Le banc est tiède. On se tait une seconde. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules nomme encore le mot, tout bas. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8092,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7867,7 +8121,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après le bus et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. On gardu geste.</t>
+          <t>Jules rejoint le soir, après le bus et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. On gardu geste.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8005,6 +8259,13 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après le bus et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules dit merci à papa. Maman sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8428,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8191,7 +8457,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Léa, après le bus. Une plume vole. On parle de Léa. Jules écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Léa, après le bus. Une plume vole. On parle de Léa. Jules écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8329,6 +8595,12 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Léa, après le bus. Une plume vole. On parle de Léa. Jules écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8515,6 +8787,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8539,7 +8816,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après le bus et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. Papa et maman sont là.</t>
+          <t>Jules rejoint le matin, après le bus et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8677,6 +8954,13 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après le bus et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules dit merci à papa. Maman sourit. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8839,6 +9123,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8863,7 +9152,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après le bus et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. On respire.</t>
+          <t>Jules rejoint après la sieste, après le bus et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules dit merci à papa. Maman sourit. On respire.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9001,6 +9290,13 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après le bus et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules dit merci à papa. Maman sourit. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9163,6 +9459,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9187,7 +9488,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après le bus et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. On laisse le soir à sa place. Jules est près de papa. Merci, et au dodo bientôt.</t>
+          <t>Jules rejoint le soir, après le bus et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. On laisse le soir à sa place. Jules est près de papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9325,6 +9626,13 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après le bus et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne. On laisse le soir à sa place.
+narrateur|Jules est près de papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9487,6 +9795,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9511,7 +9824,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Sami, après le bus. Une cloche sonne au loin. Près de Sami, Jules prend le temps. Pas de course. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Sami, après le bus. Une cloche sonne au loin. Près de Sami, Jules prend le temps. Pas de course. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9649,6 +9962,12 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Sami, après le bus. Une cloche sonne au loin. Près de Sami, Jules prend le temps. Pas de course. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9835,6 +10154,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9859,7 +10183,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après le bus et Sami. Une plume vole. On range les chaussures. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. On laisse le matin à sa place. Jules est près de papa. Le jeu peut recommencer.</t>
+          <t>Jules rejoint le matin, après le bus et Sami. Une plume vole. On range les chaussures. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. On laisse le matin à sa place. Jules est près de papa. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9997,6 +10321,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après le bus et Sami. Une plume vole. On range les chaussures. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne. On laisse le matin à sa place.
+narrateur|Jules est près de papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10159,6 +10490,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10183,7 +10519,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après le bus et Sami. Le pain croustille. On met le doudou près de soi. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. On laisse après la sieste à sa place. Jules est près de papa. On se serre un peu.</t>
+          <t>Jules rejoint après la sieste, après le bus et Sami. Le pain croustille. On met le doudou près de soi. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. On laisse après la sieste à sa place. Jules est près de papa. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10321,6 +10657,13 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après le bus et Sami. Le pain croustille. On met le doudou près de soi. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne. On laisse après la sieste à sa place.
+narrateur|Jules est près de papa. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10483,6 +10826,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10507,7 +10855,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après le bus et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. On laisse le soir à sa place. Jules est près de papa. On rentre.</t>
+          <t>Jules rejoint le soir, après le bus et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. On laisse le soir à sa place. Jules est près de papa. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10645,6 +10993,13 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après le bus et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne. On laisse le soir à sa place.
+narrateur|Jules est près de papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10807,6 +11162,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10831,7 +11191,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules a rangé près de la voiture. Il est fier de l'effort. Voilà la voiture. La fenêtre tremble un tout petit peu. Jules pose les pieds par terre, près de papa. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a rangé près de la voiture. Il est fier de l'effort. Voilà la voiture. La fenêtre tremble un tout petit peu. Jules pose les pieds par terre, près de papa. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10969,6 +11329,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a rangé près de la voiture. Il est fier de l'effort. Voilà la voiture. La fenêtre tremble un tout petit peu. Jules pose les pieds par terre, près de papa. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11151,6 +11517,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a fini un effort. Quel mot dit-on ? Avec la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11175,7 +11546,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules pose les pieds par terre. On continue, tout calme.</t>
+          <t>Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11317,6 +11688,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11885,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11531,7 +11914,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Tom, après la voiture. Un papillon passe sans bruit. Tom est là. Jules pose les mains à vue, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Tom, après la voiture. Un papillon passe sans bruit. Tom est là. Jules pose les mains à vue, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11669,6 +12052,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Tom, après la voiture. Un papillon passe sans bruit. Tom est là. Jules pose les mains à vue, loin de l'autre. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11855,6 +12244,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11879,7 +12273,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après la voiture et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. La journée continue, tout doux.</t>
+          <t>Jules rejoint le matin, après la voiture et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12017,6 +12411,13 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après la voiture et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules quitte ce moment et va vers papa. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12179,6 +12580,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12203,7 +12609,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après la voiture et Tom. Le train souffle au loin. On pose le sac. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. On se dit à plus tard.</t>
+          <t>Jules rejoint après la sieste, après la voiture et Tom. Le train souffle au loin. On pose le sac. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12341,6 +12747,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après la voiture et Tom. Le train souffle au loin. On pose le sac. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules quitte ce moment et va vers papa. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12503,6 +12916,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12527,7 +12945,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après la voiture et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules range le soir un instant. Puis il reprend, calme. Le soleil est encore là.</t>
+          <t>Jules rejoint le soir, après la voiture et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules range le soir un instant. Puis il reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12665,6 +13083,13 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après la voiture et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules range le soir un instant. Puis il reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12827,6 +13252,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12851,7 +13281,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Léa, après la voiture. Le vent glisse sur les joues. Avec Léa, Jules ralentit. Il écoute papa. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Léa, après la voiture. Le vent glisse sur les joues. Avec Léa, Jules ralentit. Il écoute papa. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12989,6 +13419,12 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Léa, après la voiture. Le vent glisse sur les joues. Avec Léa, Jules ralentit. Il écoute papa. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13175,6 +13611,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13199,7 +13640,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après la voiture et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Papa dit : je t'ai entendu. Maman aussi. On gardu geste.</t>
+          <t>Jules rejoint le matin, après la voiture et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13337,6 +13778,13 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après la voiture et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13499,6 +13947,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13523,7 +13976,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après la voiture et Léa. Le bois de la table est lisse. On attend la réponse. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Papa dit : je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+          <t>Jules rejoint après la sieste, après la voiture et Léa. Le bois de la table est lisse. On attend la réponse. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13661,6 +14114,13 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après la voiture et Léa. Le bois de la table est lisse. On attend la réponse. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13823,6 +14283,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13847,7 +14312,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après la voiture et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. On respire.</t>
+          <t>Jules rejoint le soir, après la voiture et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules quitte ce moment et va vers papa. On respire.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13985,6 +14450,13 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après la voiture et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules quitte ce moment et va vers papa. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14147,6 +14619,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14171,7 +14648,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi Sami, après la voiture. La corbeille craque. On parle de Sami. Jules écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne.</t>
+          <t>Jules a choisi Sami, après la voiture. La corbeille craque. On parle de Sami. Jules écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14309,6 +14786,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi Sami, après la voiture. La corbeille craque. On parle de Sami. Jules écoute jusqu'au bout. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14495,6 +14978,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14519,7 +15007,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le matin, après la voiture et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules boit une gorgée. Il se sent plus léger. Merci, et au dodo bientôt.</t>
+          <t>Jules rejoint le matin, après la voiture et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules boit une gorgée. Il se sent plus léger. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14657,6 +15145,13 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin, après la voiture et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules boit une gorgée. Il se sent plus léger. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14819,6 +15314,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14843,7 +15343,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint après la sieste, après la voiture et Sami. La clochette de la porte tinte. On dit stop, tout clair. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Jules boit une gorgée. Il se sent plus léger. Le jeu peut recommencer.</t>
+          <t>Jules rejoint après la sieste, après la voiture et Sami. La clochette de la porte tinte. On dit stop, tout clair. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Jules boit une gorgée. Il se sent plus léger. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14981,6 +15481,13 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste, après la voiture et Sami. La clochette de la porte tinte. On dit stop, tout clair. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+narrateur|Jules boit une gorgée. Il se sent plus léger. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15143,6 +15650,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15167,7 +15679,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le soir, après la voiture et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Jules dit : je suis fier de mon effort. Il ne rabaisse personne. Papa dit : je t'ai entendu. Maman aussi. On se serre un peu.</t>
+          <t>Jules rejoint le soir, après la voiture et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort. Je suis fier de mon effort. Il ne rabaisse personne. Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15305,6 +15817,13 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir, après la voiture et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Jules se sent fier. Le dos se redresse. C'est grâce à l'effort.
+enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.
+papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15467,6 +15986,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15485,7 +16009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15516,6 +16040,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-010.xlsx
+++ b/stories/arbres/TREE-EMO-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1326,6 +1331,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1517,6 +1523,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|Jules a fini un effort. Quel mot dit-on ? Avec le train.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2045,6 +2054,7 @@
 narrateur|Jules retient le geste. Il respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2240,6 +2250,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2408,6 +2419,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2599,6 +2611,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2768,6 +2781,7 @@
 narrateur|Jules quitte ce moment et va vers papa. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2935,6 +2949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3104,6 +3119,7 @@
 narrateur|Jules nomme encore le mot, tout bas. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3271,6 +3287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3440,6 +3457,7 @@
 narrateur|Jules boit une gorgée. Il se sent plus léger. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3607,6 +3625,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3777,6 +3796,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3968,6 +3988,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4137,6 +4158,7 @@
 narrateur|Jules serre la main de papa, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4304,6 +4326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4473,6 +4496,7 @@
 narrateur|Jules quitte ce moment et va vers papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4640,6 +4664,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4809,6 +4834,7 @@
 narrateur|Jules dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4976,6 +5002,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5144,6 +5171,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5335,6 +5363,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5504,6 +5533,7 @@
 narrateur|Jules nomme encore le mot, tout bas. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5671,6 +5701,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5840,6 +5871,7 @@
 narrateur|Jules serre la main de papa, tout doux. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6007,6 +6039,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6176,6 +6209,7 @@
 narrateur|Jules range le soir un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6343,6 +6377,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6511,6 +6546,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6698,6 +6734,7 @@
           <t>narrateur|Jules a fini un effort. Quel mot dit-on ? Avec le bus.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6871,6 +6908,7 @@
 narrateur|Jules répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7066,6 +7104,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7234,6 +7273,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7425,6 +7465,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7594,6 +7635,7 @@
 narrateur|Jules nomme encore le mot, tout bas. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7761,6 +7803,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7930,6 +7973,7 @@
 narrateur|Jules nomme encore le mot, tout bas. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8097,6 +8141,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8266,6 +8311,7 @@
 narrateur|Jules dit merci à papa. Maman sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8433,6 +8479,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8601,6 +8648,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8792,6 +8840,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8961,6 +9010,7 @@
 narrateur|Jules dit merci à papa. Maman sourit. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9128,6 +9178,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9297,6 +9348,7 @@
 narrateur|Jules dit merci à papa. Maman sourit. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9464,6 +9516,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9633,6 +9686,7 @@
 narrateur|Jules est près de papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9800,6 +9854,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9968,6 +10023,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10159,6 +10215,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10328,6 +10385,7 @@
 narrateur|Jules est près de papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10495,6 +10553,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10664,6 +10723,7 @@
 narrateur|Jules est près de papa. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10831,6 +10891,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11000,6 +11061,7 @@
 narrateur|Jules est près de papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11167,6 +11229,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11335,6 +11398,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11522,6 +11586,7 @@
           <t>narrateur|Jules a fini un effort. Quel mot dit-on ? Avec la voiture.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11695,6 +11760,7 @@
 narrateur|Jules pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11890,6 +11956,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12058,6 +12125,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12249,6 +12317,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12418,6 +12487,7 @@
 narrateur|Jules quitte ce moment et va vers papa. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12585,6 +12655,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12754,6 +12825,7 @@
 narrateur|Jules quitte ce moment et va vers papa. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12921,6 +12993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13090,6 +13163,7 @@
 narrateur|Jules range le soir un instant. Puis il reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13257,6 +13331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13425,6 +13500,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13616,6 +13692,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13785,6 +13862,7 @@
 papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13952,6 +14030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14121,6 +14200,7 @@
 papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14288,6 +14368,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14457,6 +14538,7 @@
 narrateur|Jules quitte ce moment et va vers papa. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14624,6 +14706,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14792,6 +14875,7 @@
 enfant-m|Je suis fier de mon effort. Il ne rabaisse personne.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14983,6 +15067,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15152,6 +15237,7 @@
 narrateur|Jules boit une gorgée. Il se sent plus léger. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15319,6 +15405,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15488,6 +15575,7 @@
 narrateur|Jules boit une gorgée. Il se sent plus léger. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15655,6 +15743,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15824,6 +15913,7 @@
 papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15991,6 +16081,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16009,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16047,6 +16138,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16248,6 +16353,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
